--- a/tests/traces/inference/graph_piecewise/perf_report.xlsx
+++ b/tests/traces/inference/graph_piecewise/perf_report.xlsx
@@ -1298,7 +1298,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{'elementwise', 'other'}</t>
+          <t>{'other', 'elementwise'}</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1638,7 +1638,7 @@
         <v>124885.7861328125</v>
       </c>
       <c r="O2" t="n">
-        <v>19875</v>
+        <v>19879</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>9153.9189453125</v>
       </c>
       <c r="O3" t="n">
-        <v>19486</v>
+        <v>19487</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>7556.12890625</v>
       </c>
       <c r="O4" t="n">
-        <v>19739</v>
+        <v>19743</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>1735.890625</v>
       </c>
       <c r="O6" t="n">
-        <v>19771</v>
+        <v>19775</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>1706.3291015625</v>
       </c>
       <c r="O7" t="n">
-        <v>19502</v>
+        <v>19503</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>1631.84765625</v>
       </c>
       <c r="O8" t="n">
-        <v>23835</v>
+        <v>23839</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>1566.326171875</v>
       </c>
       <c r="O9" t="n">
-        <v>19865</v>
+        <v>19869</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>591.76953125</v>
       </c>
       <c r="O10" t="n">
-        <v>19833</v>
+        <v>19837</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>435.6962890625</v>
       </c>
       <c r="O12" t="n">
-        <v>23921</v>
+        <v>23925</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>431.3720703125</v>
       </c>
       <c r="O13" t="n">
-        <v>20348</v>
+        <v>20352</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>141.5771484375</v>
       </c>
       <c r="O15" t="n">
-        <v>19941</v>
+        <v>19945</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>43.439453125</v>
       </c>
       <c r="O16" t="n">
-        <v>19396</v>
+        <v>19397</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>39.6787109375</v>
       </c>
       <c r="O17" t="n">
-        <v>19419</v>
+        <v>19420</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>125189</v>
+        <v>125273</v>
       </c>
       <c r="K2" t="n">
         <v>24</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>125190</v>
+        <v>125274</v>
       </c>
       <c r="K3" t="n">
         <v>24</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19444</v>
+        <v>19445</v>
       </c>
       <c r="K4" t="n">
         <v>24</v>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19697</v>
+        <v>19701</v>
       </c>
       <c r="K5" t="n">
         <v>24</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>125191</v>
+        <v>125275</v>
       </c>
       <c r="K7" t="n">
         <v>24</v>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>19771</v>
+        <v>19775</v>
       </c>
       <c r="K8" t="n">
         <v>24</v>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>19502</v>
+        <v>19503</v>
       </c>
       <c r="K9" t="n">
         <v>24</v>
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>23835</v>
+        <v>23839</v>
       </c>
       <c r="K10" t="n">
         <v>24</v>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19865</v>
+        <v>19869</v>
       </c>
       <c r="K11" t="n">
         <v>24</v>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>19791</v>
+        <v>19795</v>
       </c>
       <c r="K12" t="n">
         <v>24</v>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>23921</v>
+        <v>23925</v>
       </c>
       <c r="K14" t="n">
         <v>23</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>20348</v>
+        <v>20352</v>
       </c>
       <c r="K15" t="n">
         <v>24</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19941</v>
+        <v>19945</v>
       </c>
       <c r="K17" t="n">
         <v>24</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19396</v>
+        <v>19397</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19419</v>
+        <v>19420</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -7915,7 +7915,7 @@
         <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>19444</v>
+        <v>19445</v>
       </c>
     </row>
     <row r="3">
@@ -8085,7 +8085,7 @@
         <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>19486</v>
+        <v>19487</v>
       </c>
     </row>
     <row r="4">
@@ -8255,7 +8255,7 @@
         <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>19697</v>
+        <v>19701</v>
       </c>
     </row>
     <row r="5">
@@ -8425,7 +8425,7 @@
         <v>24</v>
       </c>
       <c r="AP5" t="n">
-        <v>19739</v>
+        <v>19743</v>
       </c>
     </row>
     <row r="6">
@@ -8595,7 +8595,7 @@
         <v>24</v>
       </c>
       <c r="AP6" t="n">
-        <v>19791</v>
+        <v>19795</v>
       </c>
     </row>
     <row r="7">
@@ -8765,7 +8765,7 @@
         <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>19833</v>
+        <v>19837</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +9479,7 @@
         <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>125189</v>
+        <v>125273</v>
       </c>
     </row>
     <row r="3">
@@ -9644,7 +9644,7 @@
         <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>125190</v>
+        <v>125274</v>
       </c>
     </row>
   </sheetData>
